--- a/weights/noise_injection_results.xlsx
+++ b/weights/noise_injection_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,607 +417,607 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Avg_0.4</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Std_0.4</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Min_0.4</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Max_0.4</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Avg_0.45</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Std_0.45</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Min_0.45</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Max_0.45</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Avg_0.5</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Std_0.5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Min_0.5</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Max_0.5</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Avg_0.54</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Std_0.54</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Min_0.54</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Max_0.54</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Avg_0.59</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Std_0.59</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Min_0.59</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Max_0.59</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Avg_0.64</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Std_0.64</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Min_0.64</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Max_0.64</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Avg_0.69</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Std_0.69</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Min_0.69</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Max_0.69</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Avg_0.74</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Std_0.74</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Min_0.74</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Max_0.74</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Avg_0.79</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Std_0.79</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Min_0.79</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Max_0.79</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Avg_0.83</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Std_0.83</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Min_0.83</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Max_0.83</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Avg_0.88</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Std_0.88</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Min_0.88</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Max_0.88</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Avg_0.93</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Std_0.93</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Min_0.93</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Max_0.93</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Avg_0.98</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Std_0.98</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Min_0.98</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Max_0.98</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>Avg_1.03</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>Std_1.03</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>Min_1.03</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>Max_1.03</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Avg_1.08</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Std_1.08</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>Min_1.08</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Max_1.08</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>Avg_1.12</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>Std_1.12</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>Min_1.12</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>Max_1.12</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>Avg_1.17</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>Std_1.17</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>Min_1.17</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>Max_1.17</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>Avg_1.22</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>Std_1.22</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>Min_1.22</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>Max_1.22</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>Avg_1.27</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>Std_1.27</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>Min_1.27</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>Max_1.27</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>Avg_1.32</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>Std_1.32</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>Min_1.32</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>Max_1.32</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>Avg_1.37</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>Std_1.37</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>Min_1.37</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>Max_1.37</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>Avg_1.41</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>Std_1.41</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>Min_1.41</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>Max_1.41</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>Avg_1.46</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>Std_1.46</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>Min_1.46</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>Max_1.46</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>Avg_1.51</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>Std_1.51</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>Min_1.51</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>Max_1.51</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>Avg_1.56</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>Std_1.56</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>Min_1.56</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>Max_1.56</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>Avg_1.61</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>Std_1.61</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>Min_1.61</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>Max_1.61</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>Avg_1.66</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>Std_1.66</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>Min_1.66</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>Max_1.66</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>Avg_1.7</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>Std_1.7</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>Min_1.7</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>Max_1.7</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>Avg_1.75</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>Std_1.75</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>Min_1.75</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>Max_1.75</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>Avg_1.8</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>Std_1.8</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>Min_1.8</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>Max_1.8</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>Total_Avg</t>
         </is>
@@ -1037,367 +1025,367 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3477</v>
+        <v>332.7</v>
       </c>
       <c r="B2" t="n">
-        <v>3567.421281542173</v>
+        <v>16.30981299708859</v>
       </c>
       <c r="C2" t="n">
-        <v>720</v>
+        <v>312</v>
       </c>
       <c r="D2" t="n">
-        <v>13451</v>
+        <v>373</v>
       </c>
       <c r="E2" t="n">
-        <v>2704.1</v>
+        <v>335</v>
       </c>
       <c r="F2" t="n">
-        <v>2024.932564309241</v>
+        <v>10.295630140987</v>
       </c>
       <c r="G2" t="n">
-        <v>795</v>
+        <v>312</v>
       </c>
       <c r="H2" t="n">
-        <v>8471</v>
+        <v>350</v>
       </c>
       <c r="I2" t="n">
-        <v>4161.8</v>
+        <v>329.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3680.612199077757</v>
+        <v>8.834591105421914</v>
       </c>
       <c r="K2" t="n">
-        <v>813</v>
+        <v>316</v>
       </c>
       <c r="L2" t="n">
-        <v>11527</v>
+        <v>340</v>
       </c>
       <c r="M2" t="n">
-        <v>5074</v>
+        <v>335.5</v>
       </c>
       <c r="N2" t="n">
-        <v>5548.801348039052</v>
+        <v>10.79120011861517</v>
       </c>
       <c r="O2" t="n">
-        <v>807</v>
+        <v>318</v>
       </c>
       <c r="P2" t="n">
-        <v>19721</v>
+        <v>356</v>
       </c>
       <c r="Q2" t="n">
-        <v>3785.5</v>
+        <v>339.6</v>
       </c>
       <c r="R2" t="n">
-        <v>2700.681626923099</v>
+        <v>6.086049621881176</v>
       </c>
       <c r="S2" t="n">
-        <v>266</v>
+        <v>331</v>
       </c>
       <c r="T2" t="n">
-        <v>10893</v>
+        <v>350</v>
       </c>
       <c r="U2" t="n">
-        <v>4221.1</v>
+        <v>343.9</v>
       </c>
       <c r="V2" t="n">
-        <v>2829.569947889608</v>
+        <v>18.44152922075607</v>
       </c>
       <c r="W2" t="n">
-        <v>1518</v>
+        <v>328</v>
       </c>
       <c r="X2" t="n">
-        <v>9801</v>
+        <v>393</v>
       </c>
       <c r="Y2" t="n">
-        <v>3346.9</v>
+        <v>347.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>2837.747291426776</v>
+        <v>14.66424222385869</v>
       </c>
       <c r="AA2" t="n">
-        <v>733</v>
+        <v>329</v>
       </c>
       <c r="AB2" t="n">
-        <v>8099</v>
+        <v>375</v>
       </c>
       <c r="AC2" t="n">
-        <v>3472.9</v>
+        <v>342.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>4749.843985858904</v>
+        <v>13.18180564262726</v>
       </c>
       <c r="AE2" t="n">
-        <v>721</v>
+        <v>318</v>
       </c>
       <c r="AF2" t="n">
-        <v>15899</v>
+        <v>367</v>
       </c>
       <c r="AG2" t="n">
-        <v>864.5</v>
+        <v>342.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>240.7792557509887</v>
+        <v>17.91675193778158</v>
       </c>
       <c r="AI2" t="n">
-        <v>701</v>
+        <v>315</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1550</v>
+        <v>377</v>
       </c>
       <c r="AK2" t="n">
-        <v>1978.2</v>
+        <v>350.6</v>
       </c>
       <c r="AL2" t="n">
-        <v>2058.614427230122</v>
+        <v>19.00631474010677</v>
       </c>
       <c r="AM2" t="n">
-        <v>166</v>
+        <v>326</v>
       </c>
       <c r="AN2" t="n">
-        <v>6761</v>
+        <v>395</v>
       </c>
       <c r="AO2" t="n">
-        <v>1142.6</v>
+        <v>336.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>1603.790771890149</v>
+        <v>11.63829884476249</v>
       </c>
       <c r="AQ2" t="n">
-        <v>166</v>
+        <v>322</v>
       </c>
       <c r="AR2" t="n">
-        <v>5823</v>
+        <v>363</v>
       </c>
       <c r="AS2" t="n">
-        <v>380.2</v>
+        <v>327.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>277.2031024357411</v>
+        <v>10.71634265969505</v>
       </c>
       <c r="AU2" t="n">
-        <v>171</v>
+        <v>307</v>
       </c>
       <c r="AV2" t="n">
-        <v>1199</v>
+        <v>342</v>
       </c>
       <c r="AW2" t="n">
-        <v>622.3</v>
+        <v>338</v>
       </c>
       <c r="AX2" t="n">
-        <v>630.5680058486952</v>
+        <v>20.77498495787663</v>
       </c>
       <c r="AY2" t="n">
-        <v>271</v>
+        <v>325</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2375</v>
+        <v>394</v>
       </c>
       <c r="BA2" t="n">
-        <v>276.1</v>
+        <v>334.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>49.16797738365896</v>
+        <v>11.16646765991824</v>
       </c>
       <c r="BC2" t="n">
+        <v>318</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>356</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>16.21264938250377</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>328</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>392</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>337.3</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>18.22114156687226</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>305</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>367</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>348.7</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>9.198369420718</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>332</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>362</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>252.8</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>76.47849370901601</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>191</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>398</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>201.1</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>10.18282868362225</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>184</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>219</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>205.2</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>19.98399359487487</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>180</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>253</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>203.6</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>9.551963149007642</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>183</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>219</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>35.39844629358752</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>189</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>318</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>240.9</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>54.53888521046245</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>194</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>352</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>210</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>15.88080602488425</v>
+      </c>
+      <c r="CQ2" t="n">
         <v>188</v>
       </c>
-      <c r="BD2" t="n">
-        <v>343</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1357.2</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1877.560853873983</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>202</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>5370</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>456.7</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>358.5696724487446</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>242</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1508</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>378.6</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>167.6503504320823</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>276</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>865</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>539.1</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>441.8842495495851</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>285</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1424</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>314.6</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>41.01511916354749</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>282</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>427</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>311.7</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>34.56891667379815</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>270</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>381</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>321.3</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>54.37104008569268</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>273</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>475</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>322</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>51.72813547770691</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>284</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>474</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>314.8</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>44.53942074163067</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>266</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>440</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>343.4</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>69.41930567212553</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>276</v>
-      </c>
       <c r="CR2" t="n">
-        <v>474</v>
+        <v>246</v>
       </c>
       <c r="CS2" t="n">
-        <v>319.6</v>
+        <v>269.5</v>
       </c>
       <c r="CT2" t="n">
-        <v>40.70184271012801</v>
+        <v>94.49894179301691</v>
       </c>
       <c r="CU2" t="n">
-        <v>260</v>
+        <v>191</v>
       </c>
       <c r="CV2" t="n">
-        <v>403</v>
+        <v>433</v>
       </c>
       <c r="CW2" t="n">
-        <v>342.3</v>
+        <v>300.2</v>
       </c>
       <c r="CX2" t="n">
-        <v>66.02582827954527</v>
+        <v>74.18059045329849</v>
       </c>
       <c r="CY2" t="n">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="CZ2" t="n">
-        <v>507</v>
+        <v>399</v>
       </c>
       <c r="DA2" t="n">
-        <v>317.8</v>
+        <v>362.2</v>
       </c>
       <c r="DB2" t="n">
-        <v>34.8648820448313</v>
+        <v>54.29696124093871</v>
       </c>
       <c r="DC2" t="n">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="DD2" t="n">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="DE2" t="n">
-        <v>319.9</v>
+        <v>334.4</v>
       </c>
       <c r="DF2" t="n">
-        <v>39.06520190655618</v>
+        <v>75.80659601908003</v>
       </c>
       <c r="DG2" t="n">
-        <v>251</v>
+        <v>189</v>
       </c>
       <c r="DH2" t="n">
+        <v>406</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>357.4</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>45.48889974488281</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>227</v>
+      </c>
+      <c r="DL2" t="n">
         <v>394</v>
       </c>
-      <c r="DI2" t="n">
-        <v>312.2</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>70.2307624905212</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>229</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>494</v>
-      </c>
       <c r="DM2" t="n">
-        <v>337.9</v>
+        <v>280.8</v>
       </c>
       <c r="DN2" t="n">
-        <v>64.48325363999555</v>
+        <v>75.78495892985624</v>
       </c>
       <c r="DO2" t="n">
-        <v>242</v>
+        <v>173</v>
       </c>
       <c r="DP2" t="n">
-        <v>500</v>
+        <v>374</v>
       </c>
       <c r="DQ2" t="n">
-        <v>42116.3</v>
+        <v>9207.599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/weights/noise_injection_results.xlsx
+++ b/weights/noise_injection_results.xlsx
@@ -1025,367 +1025,367 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>332.7</v>
+        <v>856.1</v>
       </c>
       <c r="B2" t="n">
-        <v>16.30981299708859</v>
+        <v>1447.102653580595</v>
       </c>
       <c r="C2" t="n">
-        <v>312</v>
+        <v>122</v>
       </c>
       <c r="D2" t="n">
-        <v>373</v>
+        <v>5017</v>
       </c>
       <c r="E2" t="n">
-        <v>335</v>
+        <v>1287.6</v>
       </c>
       <c r="F2" t="n">
-        <v>10.295630140987</v>
+        <v>2334.751173037504</v>
       </c>
       <c r="G2" t="n">
-        <v>312</v>
+        <v>114</v>
       </c>
       <c r="H2" t="n">
-        <v>350</v>
+        <v>5991</v>
       </c>
       <c r="I2" t="n">
-        <v>329.5</v>
+        <v>748.9</v>
       </c>
       <c r="J2" t="n">
-        <v>8.834591105421914</v>
+        <v>1872.3691115803</v>
       </c>
       <c r="K2" t="n">
-        <v>316</v>
+        <v>121</v>
       </c>
       <c r="L2" t="n">
-        <v>340</v>
+        <v>6366</v>
       </c>
       <c r="M2" t="n">
-        <v>335.5</v>
+        <v>1939.8</v>
       </c>
       <c r="N2" t="n">
-        <v>10.79120011861517</v>
+        <v>2978.420413574954</v>
       </c>
       <c r="O2" t="n">
-        <v>318</v>
+        <v>120</v>
       </c>
       <c r="P2" t="n">
-        <v>356</v>
+        <v>7871</v>
       </c>
       <c r="Q2" t="n">
-        <v>339.6</v>
+        <v>924.9</v>
       </c>
       <c r="R2" t="n">
-        <v>6.086049621881176</v>
+        <v>2395.702921899959</v>
       </c>
       <c r="S2" t="n">
-        <v>331</v>
+        <v>122</v>
       </c>
       <c r="T2" t="n">
-        <v>350</v>
+        <v>8112</v>
       </c>
       <c r="U2" t="n">
-        <v>343.9</v>
+        <v>1486.4</v>
       </c>
       <c r="V2" t="n">
-        <v>18.44152922075607</v>
+        <v>2951.543975616829</v>
       </c>
       <c r="W2" t="n">
-        <v>328</v>
+        <v>120</v>
       </c>
       <c r="X2" t="n">
-        <v>393</v>
+        <v>9477</v>
       </c>
       <c r="Y2" t="n">
-        <v>347.6</v>
+        <v>1281.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.66424222385869</v>
+        <v>3460.57258412535</v>
       </c>
       <c r="AA2" t="n">
-        <v>329</v>
+        <v>121</v>
       </c>
       <c r="AB2" t="n">
-        <v>375</v>
+        <v>11663</v>
       </c>
       <c r="AC2" t="n">
-        <v>342.8</v>
+        <v>128.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.18180564262726</v>
+        <v>5.499090833947008</v>
       </c>
       <c r="AE2" t="n">
-        <v>318</v>
+        <v>123</v>
       </c>
       <c r="AF2" t="n">
-        <v>367</v>
+        <v>142</v>
       </c>
       <c r="AG2" t="n">
-        <v>342.3</v>
+        <v>126.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.91675193778158</v>
+        <v>4.363484845854286</v>
       </c>
       <c r="AI2" t="n">
-        <v>315</v>
+        <v>121</v>
       </c>
       <c r="AJ2" t="n">
-        <v>377</v>
+        <v>137</v>
       </c>
       <c r="AK2" t="n">
-        <v>350.6</v>
+        <v>131.1</v>
       </c>
       <c r="AL2" t="n">
-        <v>19.00631474010677</v>
+        <v>3.534119409414458</v>
       </c>
       <c r="AM2" t="n">
-        <v>326</v>
+        <v>127</v>
       </c>
       <c r="AN2" t="n">
-        <v>395</v>
+        <v>137</v>
       </c>
       <c r="AO2" t="n">
-        <v>336.5</v>
+        <v>131.1</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.63829884476249</v>
+        <v>4.742362280551751</v>
       </c>
       <c r="AQ2" t="n">
-        <v>322</v>
+        <v>126</v>
       </c>
       <c r="AR2" t="n">
-        <v>363</v>
+        <v>141</v>
       </c>
       <c r="AS2" t="n">
-        <v>327.6</v>
+        <v>1712.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.71634265969505</v>
+        <v>4749.570423733077</v>
       </c>
       <c r="AU2" t="n">
-        <v>307</v>
+        <v>124</v>
       </c>
       <c r="AV2" t="n">
-        <v>342</v>
+        <v>15961</v>
       </c>
       <c r="AW2" t="n">
-        <v>338</v>
+        <v>130.1</v>
       </c>
       <c r="AX2" t="n">
-        <v>20.77498495787663</v>
+        <v>2.256102834535695</v>
       </c>
       <c r="AY2" t="n">
-        <v>325</v>
+        <v>126</v>
       </c>
       <c r="AZ2" t="n">
-        <v>394</v>
+        <v>132</v>
       </c>
       <c r="BA2" t="n">
-        <v>334.9</v>
+        <v>133.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>11.16646765991824</v>
+        <v>5.571355310873648</v>
       </c>
       <c r="BC2" t="n">
-        <v>318</v>
+        <v>126</v>
       </c>
       <c r="BD2" t="n">
-        <v>356</v>
+        <v>143</v>
       </c>
       <c r="BE2" t="n">
-        <v>352.5</v>
+        <v>136.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>16.21264938250377</v>
+        <v>5.970762095411271</v>
       </c>
       <c r="BG2" t="n">
-        <v>328</v>
+        <v>129</v>
       </c>
       <c r="BH2" t="n">
-        <v>392</v>
+        <v>146</v>
       </c>
       <c r="BI2" t="n">
-        <v>337.3</v>
+        <v>138.6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>18.22114156687226</v>
+        <v>7.48598690888516</v>
       </c>
       <c r="BK2" t="n">
-        <v>305</v>
+        <v>126</v>
       </c>
       <c r="BL2" t="n">
-        <v>367</v>
+        <v>153</v>
       </c>
       <c r="BM2" t="n">
-        <v>348.7</v>
+        <v>142.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>9.198369420718</v>
+        <v>7.939773296511683</v>
       </c>
       <c r="BO2" t="n">
-        <v>332</v>
+        <v>131</v>
       </c>
       <c r="BP2" t="n">
-        <v>362</v>
+        <v>156</v>
       </c>
       <c r="BQ2" t="n">
-        <v>252.8</v>
+        <v>563.1</v>
       </c>
       <c r="BR2" t="n">
-        <v>76.47849370901601</v>
+        <v>1257.642353771532</v>
       </c>
       <c r="BS2" t="n">
-        <v>191</v>
+        <v>135</v>
       </c>
       <c r="BT2" t="n">
-        <v>398</v>
+        <v>4336</v>
       </c>
       <c r="BU2" t="n">
-        <v>201.1</v>
+        <v>141.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>10.18282868362225</v>
+        <v>7.44043009509531</v>
       </c>
       <c r="BW2" t="n">
-        <v>184</v>
+        <v>134</v>
       </c>
       <c r="BX2" t="n">
-        <v>219</v>
+        <v>156</v>
       </c>
       <c r="BY2" t="n">
-        <v>205.2</v>
+        <v>1169.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>19.98399359487487</v>
+        <v>3067.206814024773</v>
       </c>
       <c r="CA2" t="n">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="CB2" t="n">
-        <v>253</v>
+        <v>10371</v>
       </c>
       <c r="CC2" t="n">
-        <v>203.6</v>
+        <v>137.7</v>
       </c>
       <c r="CD2" t="n">
-        <v>9.551963149007642</v>
+        <v>7.668767828015137</v>
       </c>
       <c r="CE2" t="n">
-        <v>183</v>
+        <v>125</v>
       </c>
       <c r="CF2" t="n">
-        <v>219</v>
+        <v>149</v>
       </c>
       <c r="CG2" t="n">
-        <v>214.5</v>
+        <v>147.6</v>
       </c>
       <c r="CH2" t="n">
-        <v>35.39844629358752</v>
+        <v>39.5454169278818</v>
       </c>
       <c r="CI2" t="n">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="CJ2" t="n">
-        <v>318</v>
+        <v>266</v>
       </c>
       <c r="CK2" t="n">
-        <v>240.9</v>
+        <v>133.3</v>
       </c>
       <c r="CL2" t="n">
-        <v>54.53888521046245</v>
+        <v>6.797793759742936</v>
       </c>
       <c r="CM2" t="n">
-        <v>194</v>
+        <v>119</v>
       </c>
       <c r="CN2" t="n">
-        <v>352</v>
+        <v>143</v>
       </c>
       <c r="CO2" t="n">
-        <v>210</v>
+        <v>134.5</v>
       </c>
       <c r="CP2" t="n">
-        <v>15.88080602488425</v>
+        <v>6.917369442208505</v>
       </c>
       <c r="CQ2" t="n">
-        <v>188</v>
+        <v>122</v>
       </c>
       <c r="CR2" t="n">
-        <v>246</v>
+        <v>147</v>
       </c>
       <c r="CS2" t="n">
-        <v>269.5</v>
+        <v>131.4</v>
       </c>
       <c r="CT2" t="n">
-        <v>94.49894179301691</v>
+        <v>6.560487786742691</v>
       </c>
       <c r="CU2" t="n">
-        <v>191</v>
+        <v>121</v>
       </c>
       <c r="CV2" t="n">
-        <v>433</v>
+        <v>140</v>
       </c>
       <c r="CW2" t="n">
-        <v>300.2</v>
+        <v>130.1</v>
       </c>
       <c r="CX2" t="n">
-        <v>74.18059045329849</v>
+        <v>6.640030120413611</v>
       </c>
       <c r="CY2" t="n">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="CZ2" t="n">
-        <v>399</v>
+        <v>144</v>
       </c>
       <c r="DA2" t="n">
-        <v>362.2</v>
+        <v>127.9</v>
       </c>
       <c r="DB2" t="n">
-        <v>54.29696124093871</v>
+        <v>6.236184731067546</v>
       </c>
       <c r="DC2" t="n">
-        <v>216</v>
+        <v>116</v>
       </c>
       <c r="DD2" t="n">
-        <v>412</v>
+        <v>137</v>
       </c>
       <c r="DE2" t="n">
-        <v>334.4</v>
+        <v>129</v>
       </c>
       <c r="DF2" t="n">
-        <v>75.80659601908003</v>
+        <v>8.567379996241558</v>
       </c>
       <c r="DG2" t="n">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="DH2" t="n">
-        <v>406</v>
+        <v>144</v>
       </c>
       <c r="DI2" t="n">
-        <v>357.4</v>
+        <v>124.4</v>
       </c>
       <c r="DJ2" t="n">
-        <v>45.48889974488281</v>
+        <v>4.715930449020639</v>
       </c>
       <c r="DK2" t="n">
-        <v>227</v>
+        <v>119</v>
       </c>
       <c r="DL2" t="n">
-        <v>394</v>
+        <v>135</v>
       </c>
       <c r="DM2" t="n">
-        <v>280.8</v>
+        <v>125.6</v>
       </c>
       <c r="DN2" t="n">
-        <v>75.78495892985624</v>
+        <v>6.873136110975834</v>
       </c>
       <c r="DO2" t="n">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="DP2" t="n">
-        <v>374</v>
+        <v>135</v>
       </c>
       <c r="DQ2" t="n">
-        <v>9207.599999999999</v>
+        <v>14630.9</v>
       </c>
     </row>
   </sheetData>

--- a/weights/noise_injection_results.xlsx
+++ b/weights/noise_injection_results.xlsx
@@ -1025,367 +1025,367 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>856.1</v>
+        <v>505.5</v>
       </c>
       <c r="B2" t="n">
-        <v>1447.102653580595</v>
+        <v>1.746424919657298</v>
       </c>
       <c r="C2" t="n">
-        <v>122</v>
+        <v>504</v>
       </c>
       <c r="D2" t="n">
-        <v>5017</v>
+        <v>508</v>
       </c>
       <c r="E2" t="n">
-        <v>1287.6</v>
+        <v>520.1</v>
       </c>
       <c r="F2" t="n">
-        <v>2334.751173037504</v>
+        <v>24.27529608470306</v>
       </c>
       <c r="G2" t="n">
-        <v>114</v>
+        <v>504</v>
       </c>
       <c r="H2" t="n">
-        <v>5991</v>
+        <v>586</v>
       </c>
       <c r="I2" t="n">
-        <v>748.9</v>
+        <v>2624.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1872.3691115803</v>
+        <v>3197.872575635246</v>
       </c>
       <c r="K2" t="n">
-        <v>121</v>
+        <v>506</v>
       </c>
       <c r="L2" t="n">
-        <v>6366</v>
+        <v>7749</v>
       </c>
       <c r="M2" t="n">
-        <v>1939.8</v>
+        <v>5651.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2978.420413574954</v>
+        <v>2978.779051893577</v>
       </c>
       <c r="O2" t="n">
-        <v>120</v>
+        <v>626</v>
       </c>
       <c r="P2" t="n">
-        <v>7871</v>
+        <v>8653</v>
       </c>
       <c r="Q2" t="n">
-        <v>924.9</v>
+        <v>1003.1</v>
       </c>
       <c r="R2" t="n">
-        <v>2395.702921899959</v>
+        <v>1393.665271864087</v>
       </c>
       <c r="S2" t="n">
-        <v>122</v>
+        <v>507</v>
       </c>
       <c r="T2" t="n">
-        <v>8112</v>
+        <v>5182</v>
       </c>
       <c r="U2" t="n">
-        <v>1486.4</v>
+        <v>509.6</v>
       </c>
       <c r="V2" t="n">
-        <v>2951.543975616829</v>
+        <v>9.340235543068493</v>
       </c>
       <c r="W2" t="n">
-        <v>120</v>
+        <v>505</v>
       </c>
       <c r="X2" t="n">
-        <v>9477</v>
+        <v>537</v>
       </c>
       <c r="Y2" t="n">
-        <v>1281.3</v>
+        <v>705.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>3460.57258412535</v>
+        <v>587.077643927956</v>
       </c>
       <c r="AA2" t="n">
-        <v>121</v>
+        <v>505</v>
       </c>
       <c r="AB2" t="n">
-        <v>11663</v>
+        <v>2467</v>
       </c>
       <c r="AC2" t="n">
-        <v>128.4</v>
+        <v>718.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.499090833947008</v>
+        <v>632.074331071908</v>
       </c>
       <c r="AE2" t="n">
-        <v>123</v>
+        <v>505</v>
       </c>
       <c r="AF2" t="n">
-        <v>142</v>
+        <v>2615</v>
       </c>
       <c r="AG2" t="n">
-        <v>126.6</v>
+        <v>782</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.363484845854286</v>
+        <v>826.3337098291464</v>
       </c>
       <c r="AI2" t="n">
-        <v>121</v>
+        <v>505</v>
       </c>
       <c r="AJ2" t="n">
-        <v>137</v>
+        <v>3261</v>
       </c>
       <c r="AK2" t="n">
-        <v>131.1</v>
+        <v>790</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.534119409414458</v>
+        <v>851.6671885190834</v>
       </c>
       <c r="AM2" t="n">
-        <v>127</v>
+        <v>505</v>
       </c>
       <c r="AN2" t="n">
-        <v>137</v>
+        <v>3345</v>
       </c>
       <c r="AO2" t="n">
-        <v>131.1</v>
+        <v>505.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.742362280551751</v>
+        <v>0.9165151389911679</v>
       </c>
       <c r="AQ2" t="n">
-        <v>126</v>
+        <v>505</v>
       </c>
       <c r="AR2" t="n">
-        <v>141</v>
+        <v>507</v>
       </c>
       <c r="AS2" t="n">
-        <v>1712.3</v>
+        <v>508.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>4749.570423733077</v>
+        <v>3.693237062523878</v>
       </c>
       <c r="AU2" t="n">
-        <v>124</v>
+        <v>505</v>
       </c>
       <c r="AV2" t="n">
-        <v>15961</v>
+        <v>515</v>
       </c>
       <c r="AW2" t="n">
-        <v>130.1</v>
+        <v>3853.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.256102834535695</v>
+        <v>2700.790299153194</v>
       </c>
       <c r="AY2" t="n">
-        <v>126</v>
+        <v>509</v>
       </c>
       <c r="AZ2" t="n">
-        <v>132</v>
+        <v>6476</v>
       </c>
       <c r="BA2" t="n">
-        <v>133.4</v>
+        <v>8802.200000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.571355310873648</v>
+        <v>3116.045404033773</v>
       </c>
       <c r="BC2" t="n">
-        <v>126</v>
+        <v>6330</v>
       </c>
       <c r="BD2" t="n">
-        <v>143</v>
+        <v>14363</v>
       </c>
       <c r="BE2" t="n">
-        <v>136.5</v>
+        <v>9816.299999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.970762095411271</v>
+        <v>3309.220060678951</v>
       </c>
       <c r="BG2" t="n">
-        <v>129</v>
+        <v>6360</v>
       </c>
       <c r="BH2" t="n">
-        <v>146</v>
+        <v>14515</v>
       </c>
       <c r="BI2" t="n">
-        <v>138.6</v>
+        <v>9207.9</v>
       </c>
       <c r="BJ2" t="n">
-        <v>7.48598690888516</v>
+        <v>3490.980706048087</v>
       </c>
       <c r="BK2" t="n">
-        <v>126</v>
+        <v>6744</v>
       </c>
       <c r="BL2" t="n">
-        <v>153</v>
+        <v>16247</v>
       </c>
       <c r="BM2" t="n">
-        <v>142.6</v>
+        <v>7734.4</v>
       </c>
       <c r="BN2" t="n">
-        <v>7.939773296511683</v>
+        <v>2065.909107390739</v>
       </c>
       <c r="BO2" t="n">
-        <v>131</v>
+        <v>6341</v>
       </c>
       <c r="BP2" t="n">
-        <v>156</v>
+        <v>13869</v>
       </c>
       <c r="BQ2" t="n">
-        <v>563.1</v>
+        <v>8075.7</v>
       </c>
       <c r="BR2" t="n">
-        <v>1257.642353771532</v>
+        <v>2131.667706280695</v>
       </c>
       <c r="BS2" t="n">
-        <v>135</v>
+        <v>6850</v>
       </c>
       <c r="BT2" t="n">
-        <v>4336</v>
+        <v>14305</v>
       </c>
       <c r="BU2" t="n">
-        <v>141.2</v>
+        <v>12738.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>7.44043009509531</v>
+        <v>4432.343363278617</v>
       </c>
       <c r="BW2" t="n">
-        <v>134</v>
+        <v>7008</v>
       </c>
       <c r="BX2" t="n">
-        <v>156</v>
+        <v>18046</v>
       </c>
       <c r="BY2" t="n">
-        <v>1169.4</v>
+        <v>12386.7</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3067.206814024773</v>
+        <v>4492.640783548135</v>
       </c>
       <c r="CA2" t="n">
-        <v>139</v>
+        <v>7094</v>
       </c>
       <c r="CB2" t="n">
-        <v>10371</v>
+        <v>18489</v>
       </c>
       <c r="CC2" t="n">
-        <v>137.7</v>
+        <v>12488.7</v>
       </c>
       <c r="CD2" t="n">
-        <v>7.668767828015137</v>
+        <v>4314.23344407787</v>
       </c>
       <c r="CE2" t="n">
-        <v>125</v>
+        <v>7332</v>
       </c>
       <c r="CF2" t="n">
-        <v>149</v>
+        <v>19297</v>
       </c>
       <c r="CG2" t="n">
-        <v>147.6</v>
+        <v>14732.1</v>
       </c>
       <c r="CH2" t="n">
-        <v>39.5454169278818</v>
+        <v>5001.260170197107</v>
       </c>
       <c r="CI2" t="n">
-        <v>130</v>
+        <v>9895</v>
       </c>
       <c r="CJ2" t="n">
-        <v>266</v>
+        <v>26006</v>
       </c>
       <c r="CK2" t="n">
-        <v>133.3</v>
+        <v>12241.9</v>
       </c>
       <c r="CL2" t="n">
-        <v>6.797793759742936</v>
+        <v>3508.336883767008</v>
       </c>
       <c r="CM2" t="n">
-        <v>119</v>
+        <v>6218</v>
       </c>
       <c r="CN2" t="n">
-        <v>143</v>
+        <v>16391</v>
       </c>
       <c r="CO2" t="n">
-        <v>134.5</v>
+        <v>13984.4</v>
       </c>
       <c r="CP2" t="n">
-        <v>6.917369442208505</v>
+        <v>6324.870610534258</v>
       </c>
       <c r="CQ2" t="n">
-        <v>122</v>
+        <v>608</v>
       </c>
       <c r="CR2" t="n">
-        <v>147</v>
+        <v>19597</v>
       </c>
       <c r="CS2" t="n">
-        <v>131.4</v>
+        <v>14493.5</v>
       </c>
       <c r="CT2" t="n">
-        <v>6.560487786742691</v>
+        <v>6278.264589040509</v>
       </c>
       <c r="CU2" t="n">
-        <v>121</v>
+        <v>399</v>
       </c>
       <c r="CV2" t="n">
-        <v>140</v>
+        <v>21251</v>
       </c>
       <c r="CW2" t="n">
-        <v>130.1</v>
+        <v>13399.5</v>
       </c>
       <c r="CX2" t="n">
-        <v>6.640030120413611</v>
+        <v>6123.221933753504</v>
       </c>
       <c r="CY2" t="n">
-        <v>118</v>
+        <v>5298</v>
       </c>
       <c r="CZ2" t="n">
-        <v>144</v>
+        <v>20797</v>
       </c>
       <c r="DA2" t="n">
-        <v>127.9</v>
+        <v>7866.8</v>
       </c>
       <c r="DB2" t="n">
-        <v>6.236184731067546</v>
+        <v>7549.542698733481</v>
       </c>
       <c r="DC2" t="n">
-        <v>116</v>
+        <v>380</v>
       </c>
       <c r="DD2" t="n">
-        <v>137</v>
+        <v>27302</v>
       </c>
       <c r="DE2" t="n">
-        <v>129</v>
+        <v>5796.4</v>
       </c>
       <c r="DF2" t="n">
-        <v>8.567379996241558</v>
+        <v>2239.328122451017</v>
       </c>
       <c r="DG2" t="n">
-        <v>116</v>
+        <v>342</v>
       </c>
       <c r="DH2" t="n">
-        <v>144</v>
+        <v>9109</v>
       </c>
       <c r="DI2" t="n">
-        <v>124.4</v>
+        <v>8668</v>
       </c>
       <c r="DJ2" t="n">
-        <v>4.715930449020639</v>
+        <v>5254.583370734544</v>
       </c>
       <c r="DK2" t="n">
-        <v>119</v>
+        <v>397</v>
       </c>
       <c r="DL2" t="n">
-        <v>135</v>
+        <v>21951</v>
       </c>
       <c r="DM2" t="n">
-        <v>125.6</v>
+        <v>9181.4</v>
       </c>
       <c r="DN2" t="n">
-        <v>6.873136110975834</v>
+        <v>12797.86800369499</v>
       </c>
       <c r="DO2" t="n">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="DP2" t="n">
-        <v>135</v>
+        <v>33286</v>
       </c>
       <c r="DQ2" t="n">
-        <v>14630.9</v>
+        <v>200292.8</v>
       </c>
     </row>
   </sheetData>
